--- a/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3006  SEMI Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3006  SEMI Wyden UniRuy 2026_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95AA7714-1694-42EB-BEA7-617D992DE688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D944FC-58DB-4113-A4FF-633D5FC4A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -674,7 +674,7 @@
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>10</v>
@@ -686,15 +686,15 @@
         <v>0.3</v>
       </c>
       <c r="G2" s="5">
-        <f>C2/7*4</f>
-        <v>0</v>
+        <f>C2/8*4</f>
+        <v>2</v>
       </c>
       <c r="H2" s="11">
         <v>0</v>
       </c>
       <c r="I2" s="6">
         <f>G2+H2</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="10" t="s">
         <v>13</v>
